--- a/artfynd/A 60589-2025 artfynd.xlsx
+++ b/artfynd/A 60589-2025 artfynd.xlsx
@@ -1260,45 +1260,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130111395</v>
+        <v>130111555</v>
       </c>
       <c r="B7" t="n">
-        <v>97705</v>
+        <v>57738</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221946</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>470886</v>
+        <v>470947</v>
       </c>
       <c r="R7" t="n">
-        <v>6539090</v>
+        <v>6538907</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1330,7 +1335,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1345,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska födohack på död avbruten gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,50 +1377,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130111555</v>
+        <v>130111395</v>
       </c>
       <c r="B8" t="n">
-        <v>57738</v>
+        <v>97707</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>221946</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>470947</v>
+        <v>470886</v>
       </c>
       <c r="R8" t="n">
-        <v>6538907</v>
+        <v>6539090</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1442,7 +1447,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,12 +1457,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:57</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska födohack på död avbruten gran.</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 60589-2025 artfynd.xlsx
+++ b/artfynd/A 60589-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130005289</v>
       </c>
       <c r="B2" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>130005860</v>
       </c>
       <c r="B3" t="n">
-        <v>56931</v>
+        <v>57016</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>130008089</v>
       </c>
       <c r="B4" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>130006116</v>
       </c>
       <c r="B5" t="n">
-        <v>56931</v>
+        <v>57016</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>130111482</v>
       </c>
       <c r="B6" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1260,50 +1260,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130111555</v>
+        <v>130111395</v>
       </c>
       <c r="B7" t="n">
-        <v>57738</v>
+        <v>97794</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>221946</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>470947</v>
+        <v>470886</v>
       </c>
       <c r="R7" t="n">
-        <v>6538907</v>
+        <v>6539090</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1335,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1345,12 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:57</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska födohack på död avbruten gran.</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,45 +1367,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130111395</v>
+        <v>130111555</v>
       </c>
       <c r="B8" t="n">
-        <v>97707</v>
+        <v>57823</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221946</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>470886</v>
+        <v>470947</v>
       </c>
       <c r="R8" t="n">
-        <v>6539090</v>
+        <v>6538907</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1447,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1457,7 +1452,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska födohack på död avbruten gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,7 +1487,7 @@
         <v>130111747</v>
       </c>
       <c r="B9" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>130111348</v>
       </c>
       <c r="B10" t="n">
-        <v>56931</v>
+        <v>57016</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 60589-2025 artfynd.xlsx
+++ b/artfynd/A 60589-2025 artfynd.xlsx
@@ -3245,10 +3245,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130322423</v>
+        <v>130321917</v>
       </c>
       <c r="B24" t="n">
-        <v>5197</v>
+        <v>57016</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3256,39 +3256,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>105930</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Spångmossen, Spångmossen, Vg</t>
+          <t>Åsmossevägen N, Vargaviddernas naturreservat, Vg</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>470869</v>
+        <v>470917</v>
       </c>
       <c r="R24" t="n">
-        <v>6538828</v>
+        <v>6538977</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3320,7 +3320,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3330,12 +3330,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre gnag och kläckhål</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3350,22 +3345,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130321917</v>
+        <v>130322423</v>
       </c>
       <c r="B25" t="n">
-        <v>57016</v>
+        <v>5197</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3373,39 +3368,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>105930</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Åsmossevägen N, Vargaviddernas naturreservat, Vg</t>
+          <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>470917</v>
+        <v>470869</v>
       </c>
       <c r="R25" t="n">
-        <v>6538977</v>
+        <v>6538828</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3437,7 +3432,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3447,7 +3442,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Äldre gnag och kläckhål</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3462,12 +3462,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>

--- a/artfynd/A 60589-2025 artfynd.xlsx
+++ b/artfynd/A 60589-2025 artfynd.xlsx
@@ -3245,10 +3245,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130321917</v>
+        <v>130322423</v>
       </c>
       <c r="B24" t="n">
-        <v>57016</v>
+        <v>5197</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3256,39 +3256,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>105930</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Åsmossevägen N, Vargaviddernas naturreservat, Vg</t>
+          <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>470917</v>
+        <v>470869</v>
       </c>
       <c r="R24" t="n">
-        <v>6538977</v>
+        <v>6538828</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3320,7 +3320,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3330,7 +3330,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre gnag och kläckhål</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3345,22 +3350,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130322423</v>
+        <v>130321917</v>
       </c>
       <c r="B25" t="n">
-        <v>5197</v>
+        <v>57016</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3368,39 +3373,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>105930</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Spångmossen, Spångmossen, Vg</t>
+          <t>Åsmossevägen N, Vargaviddernas naturreservat, Vg</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>470869</v>
+        <v>470917</v>
       </c>
       <c r="R25" t="n">
-        <v>6538828</v>
+        <v>6538977</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3432,7 +3437,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3442,12 +3447,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Äldre gnag och kläckhål</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3462,12 +3462,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>

--- a/artfynd/A 60589-2025 artfynd.xlsx
+++ b/artfynd/A 60589-2025 artfynd.xlsx
@@ -1380,7 +1380,7 @@
         <v>130111395</v>
       </c>
       <c r="B8" t="n">
-        <v>97794</v>
+        <v>97797</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1484,50 +1484,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130111348</v>
+        <v>130111747</v>
       </c>
       <c r="B9" t="n">
-        <v>57016</v>
+        <v>57826</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>470794</v>
+        <v>470957</v>
       </c>
       <c r="R9" t="n">
-        <v>6539043</v>
+        <v>6538861</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1559,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1569,12 +1564,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På sten</t>
+          <t>Rikligt med färska hackringar med savflöde på tall med turkos sveaskogssnitsel på.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1601,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130111747</v>
+        <v>130322056</v>
       </c>
       <c r="B10" t="n">
-        <v>57826</v>
+        <v>57823</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1612,16 +1607,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1630,16 +1625,21 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>470957</v>
+        <v>470903</v>
       </c>
       <c r="R10" t="n">
-        <v>6538861</v>
+        <v>6538991</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1666,27 +1666,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Rikligt med färska hackringar med savflöde på tall med turkos sveaskogssnitsel på.</t>
+          <t>Färska födohack vid basen av död gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1713,7 +1713,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130322056</v>
+        <v>130321743</v>
       </c>
       <c r="B11" t="n">
         <v>57823</v>
@@ -1749,14 +1749,14 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Spångmossen, Spångmossen, Vg</t>
+          <t>Boramossen, Boramossen, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>470903</v>
+        <v>470831</v>
       </c>
       <c r="R11" t="n">
-        <v>6538991</v>
+        <v>6539127</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1798,12 +1798,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Färska födohack vid basen av död gran</t>
+          <t>Färska och äldre födohack på tvillingtall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1830,38 +1830,38 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130321743</v>
+        <v>130324834</v>
       </c>
       <c r="B12" t="n">
-        <v>57823</v>
+        <v>57016</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1870,10 +1870,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>470831</v>
+        <v>470844</v>
       </c>
       <c r="R12" t="n">
-        <v>6539127</v>
+        <v>6539137</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Färska och äldre födohack på tvillingtall.</t>
+          <t>På sten</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1947,38 +1947,38 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130324834</v>
+        <v>130324876</v>
       </c>
       <c r="B13" t="n">
-        <v>57016</v>
+        <v>57823</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>470844</v>
+        <v>470819</v>
       </c>
       <c r="R13" t="n">
-        <v>6539137</v>
+        <v>6539135</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2032,12 +2032,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På sten</t>
+          <t>Färska födohack på klen granlåga</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2064,38 +2064,52 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130324876</v>
+        <v>130324653</v>
       </c>
       <c r="B14" t="n">
-        <v>57823</v>
+        <v>57016</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2104,10 +2118,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>470819</v>
+        <v>470960</v>
       </c>
       <c r="R14" t="n">
-        <v>6539135</v>
+        <v>6539015</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2139,7 +2153,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2149,12 +2163,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Färska födohack på klen granlåga</t>
+          <t>Stjärtfjäder av tjädertupp</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2181,10 +2195,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130324653</v>
+        <v>130321924</v>
       </c>
       <c r="B15" t="n">
-        <v>57016</v>
+        <v>5197</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2192,53 +2206,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>105930</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Boramossen, Boramossen, Vg</t>
+          <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>470960</v>
+        <v>470911</v>
       </c>
       <c r="R15" t="n">
-        <v>6539015</v>
+        <v>6538981</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Stjärtfjäder av tjädertupp</t>
+          <t>Äldre gnag och kläckhål</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2312,10 +2312,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130321924</v>
+        <v>130321613</v>
       </c>
       <c r="B16" t="n">
-        <v>5197</v>
+        <v>4773</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2323,21 +2323,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>105930</v>
+        <v>100299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2348,14 +2348,14 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Spångmossen, Spångmossen, Vg</t>
+          <t>Boramossen, Boramossen, Vg</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>470911</v>
+        <v>470789</v>
       </c>
       <c r="R16" t="n">
-        <v>6538981</v>
+        <v>6539110</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2387,7 +2387,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Äldre gnag och kläckhål</t>
+          <t>Äldre gnagspår och kläckhål.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2429,50 +2429,53 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130321613</v>
+        <v>130322176</v>
       </c>
       <c r="B17" t="n">
-        <v>4773</v>
+        <v>57826</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100299</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Boramossen, Boramossen, Vg</t>
+          <t>Åsmossevägen N, Vargaviddernas naturreservat, Vg</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>470789</v>
+        <v>470880</v>
       </c>
       <c r="R17" t="n">
-        <v>6539110</v>
+        <v>6538994</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2504,7 +2507,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2514,12 +2517,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Äldre gnagspår och kläckhål.</t>
+          <t>Gammalt bo i avbruten gran, ca 4-5 meter högt upp</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2534,22 +2537,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130321939</v>
+        <v>130321696</v>
       </c>
       <c r="B18" t="n">
-        <v>57016</v>
+        <v>5177</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2557,39 +2560,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>100526</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Åsmossevägen N, Åsmossevägen N, Vg</t>
+          <t>Boramossen, Boramossen, Vg</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>470920</v>
+        <v>470799</v>
       </c>
       <c r="R18" t="n">
-        <v>6538957</v>
+        <v>6539107</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2621,7 +2624,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2631,7 +2634,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre gnag och kläckhål.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2646,65 +2654,62 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130322176</v>
+        <v>130322807</v>
       </c>
       <c r="B19" t="n">
-        <v>57826</v>
+        <v>5177</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Åsmossevägen N, Vargaviddernas naturreservat, Vg</t>
+          <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>470880</v>
+        <v>471012</v>
       </c>
       <c r="R19" t="n">
-        <v>6538994</v>
+        <v>6538879</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2736,7 +2741,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2746,12 +2751,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Gammalt bo i avbruten gran, ca 4-5 meter högt upp</t>
+          <t>Äldre gnag och kläckhål</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2766,22 +2771,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130321696</v>
+        <v>130324988</v>
       </c>
       <c r="B20" t="n">
-        <v>5177</v>
+        <v>93013</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2789,39 +2794,43 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100526</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Boramossen, Boramossen, Vg</t>
+          <t>Åsmossevägen N, Åsmossevägen N, Vg</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>470799</v>
+        <v>470736</v>
       </c>
       <c r="R20" t="n">
-        <v>6539107</v>
+        <v>6539110</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2853,7 +2862,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2863,12 +2872,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Äldre gnag och kläckhål.</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2883,19 +2887,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130322807</v>
+        <v>130323210</v>
       </c>
       <c r="B21" t="n">
         <v>5177</v>
@@ -2931,14 +2935,14 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Spångmossen, Spångmossen, Vg</t>
+          <t>Boramossen, Boramossen, Vg</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>471012</v>
+        <v>471119</v>
       </c>
       <c r="R21" t="n">
-        <v>6538879</v>
+        <v>6538921</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2970,7 +2974,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2980,7 +2984,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3012,10 +3016,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130324988</v>
+        <v>130322423</v>
       </c>
       <c r="B22" t="n">
-        <v>93010</v>
+        <v>5197</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3023,43 +3027,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>105930</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Åsmossevägen N, Åsmossevägen N, Vg</t>
+          <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>470736</v>
+        <v>470869</v>
       </c>
       <c r="R22" t="n">
-        <v>6539110</v>
+        <v>6538828</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3101,7 +3101,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre gnag och kläckhål</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3116,22 +3121,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130323210</v>
+        <v>130322265</v>
       </c>
       <c r="B23" t="n">
-        <v>5177</v>
+        <v>5197</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3139,21 +3144,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3164,14 +3169,14 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Boramossen, Boramossen, Vg</t>
+          <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>471119</v>
+        <v>470922</v>
       </c>
       <c r="R23" t="n">
-        <v>6538921</v>
+        <v>6538911</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3203,7 +3208,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3213,7 +3218,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3245,7 +3250,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130322423</v>
+        <v>130322826</v>
       </c>
       <c r="B24" t="n">
         <v>5197</v>
@@ -3285,10 +3290,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>470869</v>
+        <v>470996</v>
       </c>
       <c r="R24" t="n">
-        <v>6538828</v>
+        <v>6538865</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3320,7 +3325,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3330,7 +3335,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3362,10 +3367,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130321917</v>
+        <v>130322032</v>
       </c>
       <c r="B25" t="n">
-        <v>57016</v>
+        <v>4773</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3373,39 +3378,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>100299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Åsmossevägen N, Vargaviddernas naturreservat, Vg</t>
+          <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>470917</v>
+        <v>470903</v>
       </c>
       <c r="R25" t="n">
-        <v>6538977</v>
+        <v>6538991</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3437,7 +3442,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3447,7 +3452,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Äldre gnag och kläckhål</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3462,22 +3472,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130322265</v>
+        <v>130321939</v>
       </c>
       <c r="B26" t="n">
-        <v>5197</v>
+        <v>57016</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3485,39 +3495,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>105930</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Spångmossen, Spångmossen, Vg</t>
+          <t>Åsmossevägen N, Åsmossevägen N, Vg</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>470922</v>
+        <v>470920</v>
       </c>
       <c r="R26" t="n">
-        <v>6538911</v>
+        <v>6538957</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3549,7 +3559,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3559,12 +3569,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:43</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Äldre gnag och kläckhål</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3579,22 +3584,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130322826</v>
+        <v>130111348</v>
       </c>
       <c r="B27" t="n">
-        <v>5197</v>
+        <v>57016</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3602,27 +3607,27 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>105930</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3631,10 +3636,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>470996</v>
+        <v>470794</v>
       </c>
       <c r="R27" t="n">
-        <v>6538865</v>
+        <v>6539043</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3661,27 +3666,27 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Äldre gnag och kläckhål</t>
+          <t>På sten</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3708,10 +3713,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130322032</v>
+        <v>130321917</v>
       </c>
       <c r="B28" t="n">
-        <v>4773</v>
+        <v>57016</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3719,39 +3724,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100299</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Spångmossen, Spångmossen, Vg</t>
+          <t>Åsmossevägen N, Vargaviddernas naturreservat, Vg</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>470903</v>
+        <v>470917</v>
       </c>
       <c r="R28" t="n">
-        <v>6538991</v>
+        <v>6538977</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3783,7 +3788,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3793,12 +3798,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Äldre gnag och kläckhål</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3813,12 +3813,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>

--- a/artfynd/A 60589-2025 artfynd.xlsx
+++ b/artfynd/A 60589-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>130005860</v>
       </c>
       <c r="B3" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>130006116</v>
       </c>
       <c r="B5" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>130111482</v>
       </c>
       <c r="B6" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1260,50 +1260,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130111555</v>
+        <v>130111395</v>
       </c>
       <c r="B7" t="n">
-        <v>57823</v>
+        <v>97823</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>221946</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>470947</v>
+        <v>470886</v>
       </c>
       <c r="R7" t="n">
-        <v>6538907</v>
+        <v>6539090</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1335,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1345,12 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:57</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska födohack på död avbruten gran.</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,45 +1367,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130111395</v>
+        <v>130111555</v>
       </c>
       <c r="B8" t="n">
-        <v>97797</v>
+        <v>57849</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221946</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>470886</v>
+        <v>470947</v>
       </c>
       <c r="R8" t="n">
-        <v>6539090</v>
+        <v>6538907</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1447,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1457,7 +1452,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska födohack på död avbruten gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,7 +1487,7 @@
         <v>130111747</v>
       </c>
       <c r="B9" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>130322056</v>
       </c>
       <c r="B10" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>130321743</v>
       </c>
       <c r="B11" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>130324834</v>
       </c>
       <c r="B12" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         <v>130324876</v>
       </c>
       <c r="B13" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>130324653</v>
       </c>
       <c r="B14" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>130322176</v>
       </c>
       <c r="B17" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         <v>130324988</v>
       </c>
       <c r="B20" t="n">
-        <v>93013</v>
+        <v>93039</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>130321939</v>
       </c>
       <c r="B26" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>130111348</v>
       </c>
       <c r="B27" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
         <v>130321917</v>
       </c>
       <c r="B28" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 60589-2025 artfynd.xlsx
+++ b/artfynd/A 60589-2025 artfynd.xlsx
@@ -2786,7 +2786,7 @@
         <v>130324988</v>
       </c>
       <c r="B20" t="n">
-        <v>93039</v>
+        <v>93040</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 60589-2025 artfynd.xlsx
+++ b/artfynd/A 60589-2025 artfynd.xlsx
@@ -2786,7 +2786,7 @@
         <v>130324988</v>
       </c>
       <c r="B20" t="n">
-        <v>93040</v>
+        <v>93041</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 60589-2025 artfynd.xlsx
+++ b/artfynd/A 60589-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>130005860</v>
       </c>
       <c r="B3" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>130006116</v>
       </c>
       <c r="B5" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>130322056</v>
       </c>
       <c r="B10" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>130321743</v>
       </c>
       <c r="B11" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>130324834</v>
       </c>
       <c r="B12" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         <v>130324876</v>
       </c>
       <c r="B13" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>130324653</v>
       </c>
       <c r="B14" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>130322176</v>
       </c>
       <c r="B17" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         <v>130324988</v>
       </c>
       <c r="B20" t="n">
-        <v>93041</v>
+        <v>93043</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>130321939</v>
       </c>
       <c r="B26" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>130111348</v>
       </c>
       <c r="B27" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
         <v>130321917</v>
       </c>
       <c r="B28" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 60589-2025 artfynd.xlsx
+++ b/artfynd/A 60589-2025 artfynd.xlsx
@@ -2786,7 +2786,7 @@
         <v>130324988</v>
       </c>
       <c r="B20" t="n">
-        <v>93043</v>
+        <v>93047</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 60589-2025 artfynd.xlsx
+++ b/artfynd/A 60589-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>130005860</v>
       </c>
       <c r="B3" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>130006116</v>
       </c>
       <c r="B5" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>130322056</v>
       </c>
       <c r="B10" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>130321743</v>
       </c>
       <c r="B11" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>130324834</v>
       </c>
       <c r="B12" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         <v>130324876</v>
       </c>
       <c r="B13" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>130324653</v>
       </c>
       <c r="B14" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>130322176</v>
       </c>
       <c r="B17" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         <v>130324988</v>
       </c>
       <c r="B20" t="n">
-        <v>93047</v>
+        <v>93060</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>130321939</v>
       </c>
       <c r="B26" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>130111348</v>
       </c>
       <c r="B27" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
         <v>130321917</v>
       </c>
       <c r="B28" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 60589-2025 artfynd.xlsx
+++ b/artfynd/A 60589-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>130005860</v>
       </c>
       <c r="B3" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>130006116</v>
       </c>
       <c r="B5" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>130322056</v>
       </c>
       <c r="B10" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>130321743</v>
       </c>
       <c r="B11" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>130324834</v>
       </c>
       <c r="B12" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         <v>130324876</v>
       </c>
       <c r="B13" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>130324653</v>
       </c>
       <c r="B14" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>130322176</v>
       </c>
       <c r="B17" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         <v>130324988</v>
       </c>
       <c r="B20" t="n">
-        <v>93060</v>
+        <v>93061</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>130321939</v>
       </c>
       <c r="B26" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>130111348</v>
       </c>
       <c r="B27" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
         <v>130321917</v>
       </c>
       <c r="B28" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 60589-2025 artfynd.xlsx
+++ b/artfynd/A 60589-2025 artfynd.xlsx
@@ -1599,7 +1599,7 @@
         <v>130322056</v>
       </c>
       <c r="B10" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>130321743</v>
       </c>
       <c r="B11" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         <v>130324876</v>
       </c>
       <c r="B13" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>130322176</v>
       </c>
       <c r="B17" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         <v>130324988</v>
       </c>
       <c r="B20" t="n">
-        <v>93061</v>
+        <v>93062</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 60589-2025 artfynd.xlsx
+++ b/artfynd/A 60589-2025 artfynd.xlsx
@@ -2786,7 +2786,7 @@
         <v>130324988</v>
       </c>
       <c r="B20" t="n">
-        <v>93062</v>
+        <v>93071</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 60589-2025 artfynd.xlsx
+++ b/artfynd/A 60589-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130005289</v>
+        <v>130324988</v>
       </c>
       <c r="B2" t="n">
-        <v>57823</v>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,43 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Boramossen, Boramossen, Vg</t>
+          <t>Åsmossevägen N, Åsmossevägen N, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>470845</v>
+        <v>470736</v>
       </c>
       <c r="R2" t="n">
-        <v>6539084</v>
+        <v>6539110</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -745,27 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:46</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färska födohack vid basen av död gran.</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +779,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130005860</v>
+        <v>130005289</v>
       </c>
       <c r="B3" t="n">
-        <v>57073</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,39 +802,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Spångmossen, Spångmossen, Vg</t>
+          <t>Boramossen, Boramossen, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>470899</v>
+        <v>470845</v>
       </c>
       <c r="R3" t="n">
-        <v>6539002</v>
+        <v>6539084</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -867,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +876,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På sten.</t>
+          <t>Färska födohack vid basen av död gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,14 +908,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130008089</v>
+        <v>130006694</v>
       </c>
       <c r="B4" t="n">
-        <v>57823</v>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -945,14 +944,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Boramossen, Boramossen, Vg</t>
+          <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>470720</v>
+        <v>471047</v>
       </c>
       <c r="R4" t="n">
-        <v>6539108</v>
+        <v>6538890</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -984,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,12 +993,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Färska födohack på klen granlåga.</t>
+          <t>Färska födohack på tunn granlåga.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130006116</v>
+        <v>130008089</v>
       </c>
       <c r="B5" t="n">
-        <v>57073</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1037,39 +1036,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Spångmossen, Spångmossen, Vg</t>
+          <t>Boramossen, Boramossen, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>470899</v>
+        <v>470720</v>
       </c>
       <c r="R5" t="n">
-        <v>6538887</v>
+        <v>6539108</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1101,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,12 +1110,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rikligt på sten.</t>
+          <t>Färska födohack på klen granlåga.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,11 +1145,11 @@
         <v>130111482</v>
       </c>
       <c r="B6" t="n">
-        <v>57849</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1260,10 +1259,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130111395</v>
+        <v>130111555</v>
       </c>
       <c r="B7" t="n">
-        <v>97823</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,34 +1270,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221946</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>470886</v>
+        <v>470947</v>
       </c>
       <c r="R7" t="n">
-        <v>6539090</v>
+        <v>6538907</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1330,7 +1334,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1344,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska födohack på död avbruten gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,14 +1376,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130111555</v>
+        <v>130321743</v>
       </c>
       <c r="B8" t="n">
-        <v>57849</v>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1403,14 +1412,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Spångmossen, Spångmossen, Vg</t>
+          <t>Boramossen, Boramossen, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>470947</v>
+        <v>470831</v>
       </c>
       <c r="R8" t="n">
-        <v>6538907</v>
+        <v>6539127</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1437,27 +1446,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska födohack på död avbruten gran.</t>
+          <t>Färska och äldre födohack på tvillingtall.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1484,27 +1493,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130111747</v>
+        <v>130322056</v>
       </c>
       <c r="B9" t="n">
-        <v>57852</v>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1513,16 +1522,21 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>470957</v>
+        <v>470903</v>
       </c>
       <c r="R9" t="n">
-        <v>6538861</v>
+        <v>6538991</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1549,27 +1563,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Rikligt med färska hackringar med savflöde på tall med turkos sveaskogssnitsel på.</t>
+          <t>Färska födohack vid basen av död gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1596,14 +1610,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130322056</v>
+        <v>130324876</v>
       </c>
       <c r="B10" t="n">
-        <v>57861</v>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1632,14 +1646,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Spångmossen, Spångmossen, Vg</t>
+          <t>Boramossen, Boramossen, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>470903</v>
+        <v>470819</v>
       </c>
       <c r="R10" t="n">
-        <v>6538991</v>
+        <v>6539135</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1671,7 +1685,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1681,12 +1695,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Färska födohack vid basen av död gran</t>
+          <t>Färska födohack på klen granlåga</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1713,10 +1727,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130321743</v>
+        <v>130111747</v>
       </c>
       <c r="B11" t="n">
-        <v>57861</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1724,16 +1738,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1742,21 +1756,16 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Boramossen, Boramossen, Vg</t>
+          <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>470831</v>
+        <v>470957</v>
       </c>
       <c r="R11" t="n">
-        <v>6539127</v>
+        <v>6538861</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1783,27 +1792,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Färska och äldre födohack på tvillingtall.</t>
+          <t>Rikligt med färska hackringar med savflöde på tall med turkos sveaskogssnitsel på.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1830,50 +1839,53 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130324834</v>
+        <v>130322176</v>
       </c>
       <c r="B12" t="n">
-        <v>57053</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Boramossen, Boramossen, Vg</t>
+          <t>Åsmossevägen N, Vargaviddernas naturreservat, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>470844</v>
+        <v>470880</v>
       </c>
       <c r="R12" t="n">
-        <v>6539137</v>
+        <v>6538994</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1905,7 +1917,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1915,12 +1927,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På sten</t>
+          <t>Gammalt bo i avbruten gran, ca 4-5 meter högt upp</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1935,62 +1947,62 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130324876</v>
+        <v>130005860</v>
       </c>
       <c r="B13" t="n">
-        <v>57861</v>
+        <v>57141</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Boramossen, Boramossen, Vg</t>
+          <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>470819</v>
+        <v>470899</v>
       </c>
       <c r="R13" t="n">
-        <v>6539135</v>
+        <v>6539002</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2017,27 +2029,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Färska födohack på klen granlåga</t>
+          <t>På sten.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2064,10 +2076,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130324653</v>
+        <v>130006116</v>
       </c>
       <c r="B14" t="n">
-        <v>57053</v>
+        <v>57141</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2092,36 +2104,22 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Boramossen, Boramossen, Vg</t>
+          <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>470960</v>
+        <v>470899</v>
       </c>
       <c r="R14" t="n">
-        <v>6539015</v>
+        <v>6538887</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2148,27 +2146,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Stjärtfjäder av tjädertupp</t>
+          <t>Rikligt på sten.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2195,10 +2193,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130321924</v>
+        <v>130111348</v>
       </c>
       <c r="B15" t="n">
-        <v>5197</v>
+        <v>57141</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2206,27 +2204,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>105930</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2235,10 +2233,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>470911</v>
+        <v>470794</v>
       </c>
       <c r="R15" t="n">
-        <v>6538981</v>
+        <v>6539043</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2265,27 +2263,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Äldre gnag och kläckhål</t>
+          <t>På sten</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2312,10 +2310,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130321613</v>
+        <v>130111912</v>
       </c>
       <c r="B16" t="n">
-        <v>4773</v>
+        <v>57141</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2323,27 +2321,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100299</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2352,10 +2350,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>470789</v>
+        <v>471044</v>
       </c>
       <c r="R16" t="n">
-        <v>6539110</v>
+        <v>6538957</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2382,27 +2380,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Äldre gnagspår och kläckhål.</t>
+          <t>På sten</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2429,56 +2427,53 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130322176</v>
+        <v>130321685</v>
       </c>
       <c r="B17" t="n">
-        <v>57878</v>
+        <v>57141</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Åsmossevägen N, Vargaviddernas naturreservat, Vg</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>470880</v>
+        <v>470979</v>
       </c>
       <c r="R17" t="n">
-        <v>6538994</v>
+        <v>6539026</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2507,7 +2502,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2517,12 +2512,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Gammalt bo i avbruten gran, ca 4-5 meter högt upp</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2549,10 +2539,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130321696</v>
+        <v>130321917</v>
       </c>
       <c r="B18" t="n">
-        <v>5177</v>
+        <v>57141</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2560,39 +2550,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Boramossen, Boramossen, Vg</t>
+          <t>Åsmossevägen N, Vargaviddernas naturreservat, Vg</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>470799</v>
+        <v>470917</v>
       </c>
       <c r="R18" t="n">
-        <v>6539107</v>
+        <v>6538977</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2624,7 +2614,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2634,12 +2624,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre gnag och kläckhål.</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2654,22 +2639,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130322807</v>
+        <v>130321939</v>
       </c>
       <c r="B19" t="n">
-        <v>5177</v>
+        <v>57141</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2677,39 +2662,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Spångmossen, Spångmossen, Vg</t>
+          <t>Åsmossevägen N, Åsmossevägen N, Vg</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>471012</v>
+        <v>470920</v>
       </c>
       <c r="R19" t="n">
-        <v>6538879</v>
+        <v>6538957</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2741,7 +2726,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2751,12 +2736,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:09</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre gnag och kläckhål</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2771,22 +2751,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130324988</v>
+        <v>130324271</v>
       </c>
       <c r="B20" t="n">
-        <v>93089</v>
+        <v>57141</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2794,43 +2774,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Åsmossevägen N, Åsmossevägen N, Vg</t>
+          <t>Åsmossevägen N, Vargaviddernas naturreservat, Vg</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>470736</v>
+        <v>471181</v>
       </c>
       <c r="R20" t="n">
-        <v>6539110</v>
+        <v>6538991</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2862,7 +2833,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2872,7 +2843,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Fjäder från höna</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2899,10 +2875,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130323210</v>
+        <v>130324653</v>
       </c>
       <c r="B21" t="n">
-        <v>5177</v>
+        <v>57141</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2910,27 +2886,41 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2939,10 +2929,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>471119</v>
+        <v>470960</v>
       </c>
       <c r="R21" t="n">
-        <v>6538921</v>
+        <v>6539015</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2974,7 +2964,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2984,12 +2974,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Äldre gnag och kläckhål</t>
+          <t>Stjärtfjäder av tjädertupp</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3016,10 +3006,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130322423</v>
+        <v>130324834</v>
       </c>
       <c r="B22" t="n">
-        <v>5197</v>
+        <v>57141</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3027,39 +3017,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>105930</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Spångmossen, Spångmossen, Vg</t>
+          <t>Boramossen, Boramossen, Vg</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>470869</v>
+        <v>470844</v>
       </c>
       <c r="R22" t="n">
-        <v>6538828</v>
+        <v>6539137</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3091,7 +3081,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3101,12 +3091,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Äldre gnag och kläckhål</t>
+          <t>På sten</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3133,10 +3123,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130322265</v>
+        <v>130321613</v>
       </c>
       <c r="B23" t="n">
-        <v>5197</v>
+        <v>4775</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3144,21 +3134,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>105930</v>
+        <v>100299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3169,14 +3159,14 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Spångmossen, Spångmossen, Vg</t>
+          <t>Boramossen, Boramossen, Vg</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>470922</v>
+        <v>470789</v>
       </c>
       <c r="R23" t="n">
-        <v>6538911</v>
+        <v>6539110</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3208,7 +3198,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3218,12 +3208,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Äldre gnag och kläckhål</t>
+          <t>Äldre gnagspår och kläckhål.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3250,10 +3240,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130322826</v>
+        <v>130322032</v>
       </c>
       <c r="B24" t="n">
-        <v>5197</v>
+        <v>4775</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3261,21 +3251,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>105930</v>
+        <v>100299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3290,10 +3280,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>470996</v>
+        <v>470903</v>
       </c>
       <c r="R24" t="n">
-        <v>6538865</v>
+        <v>6538991</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3325,7 +3315,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3335,7 +3325,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3367,10 +3357,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130322032</v>
+        <v>130321696</v>
       </c>
       <c r="B25" t="n">
-        <v>4773</v>
+        <v>5179</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3378,21 +3368,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100299</v>
+        <v>100526</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3403,14 +3393,14 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Spångmossen, Spångmossen, Vg</t>
+          <t>Boramossen, Boramossen, Vg</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>470903</v>
+        <v>470799</v>
       </c>
       <c r="R25" t="n">
-        <v>6538991</v>
+        <v>6539107</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3442,7 +3432,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3452,12 +3442,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Äldre gnag och kläckhål</t>
+          <t>Äldre gnag och kläckhål.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3484,10 +3474,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130321939</v>
+        <v>130322807</v>
       </c>
       <c r="B26" t="n">
-        <v>57073</v>
+        <v>5179</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3495,39 +3485,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>100526</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Åsmossevägen N, Åsmossevägen N, Vg</t>
+          <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>470920</v>
+        <v>471012</v>
       </c>
       <c r="R26" t="n">
-        <v>6538957</v>
+        <v>6538879</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3559,7 +3549,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3569,7 +3559,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Äldre gnag och kläckhål</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3584,22 +3579,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130111348</v>
+        <v>130323210</v>
       </c>
       <c r="B27" t="n">
-        <v>57073</v>
+        <v>5179</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3607,39 +3602,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>100526</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Spångmossen, Spångmossen, Vg</t>
+          <t>Boramossen, Boramossen, Vg</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>470794</v>
+        <v>471119</v>
       </c>
       <c r="R27" t="n">
-        <v>6539043</v>
+        <v>6538921</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3666,27 +3661,27 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På sten</t>
+          <t>Äldre gnag och kläckhål</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3713,10 +3708,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130321917</v>
+        <v>130321924</v>
       </c>
       <c r="B28" t="n">
-        <v>57073</v>
+        <v>5199</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3724,39 +3719,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>105930</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Åsmossevägen N, Vargaviddernas naturreservat, Vg</t>
+          <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>470917</v>
+        <v>470911</v>
       </c>
       <c r="R28" t="n">
-        <v>6538977</v>
+        <v>6538981</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3788,7 +3783,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3798,7 +3793,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Äldre gnag och kläckhål</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3813,15 +3813,580 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>130322265</v>
+      </c>
+      <c r="B29" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Spångmossen, Spångmossen, Vg</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>470922</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6538911</v>
+      </c>
+      <c r="S29" t="n">
+        <v>20</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Äldre gnag och kläckhål</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>130322423</v>
+      </c>
+      <c r="B30" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Spångmossen, Spångmossen, Vg</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>470869</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6538828</v>
+      </c>
+      <c r="S30" t="n">
+        <v>20</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Äldre gnag och kläckhål</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>130322826</v>
+      </c>
+      <c r="B31" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Spångmossen, Spångmossen, Vg</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>470996</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6538865</v>
+      </c>
+      <c r="S31" t="n">
+        <v>20</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Äldre gnag och kläckhål</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>130111287</v>
+      </c>
+      <c r="B32" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Spångmossen, Spångmossen, Vg</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>470734</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6539068</v>
+      </c>
+      <c r="S32" t="n">
+        <v>20</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>130111395</v>
+      </c>
+      <c r="B33" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Spångmossen, Spångmossen, Vg</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>470886</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6539090</v>
+      </c>
+      <c r="S33" t="n">
+        <v>20</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60589-2025 artfynd.xlsx
+++ b/artfynd/A 60589-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3357,10 +3357,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130321696</v>
+        <v>130323305</v>
       </c>
       <c r="B25" t="n">
-        <v>5179</v>
+        <v>4776</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3368,21 +3368,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3393,14 +3393,14 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Boramossen, Boramossen, Vg</t>
+          <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>470799</v>
+        <v>471104</v>
       </c>
       <c r="R25" t="n">
-        <v>6539107</v>
+        <v>6538899</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Äldre gnag och kläckhål.</t>
+          <t>Äldre gnag och kläckhål</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3474,10 +3474,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130322807</v>
+        <v>130323532</v>
       </c>
       <c r="B26" t="n">
-        <v>5179</v>
+        <v>4776</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3485,21 +3485,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3510,14 +3510,14 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Spångmossen, Spångmossen, Vg</t>
+          <t>Boramossen, Boramossen, Vg</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>471012</v>
+        <v>471193</v>
       </c>
       <c r="R26" t="n">
-        <v>6538879</v>
+        <v>6538984</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3549,7 +3549,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3591,10 +3591,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130323210</v>
+        <v>130324686</v>
       </c>
       <c r="B27" t="n">
-        <v>5179</v>
+        <v>4776</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3602,21 +3602,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3631,10 +3631,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>471119</v>
+        <v>470954</v>
       </c>
       <c r="R27" t="n">
-        <v>6538921</v>
+        <v>6538994</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3708,10 +3708,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130321924</v>
+        <v>130321696</v>
       </c>
       <c r="B28" t="n">
-        <v>5199</v>
+        <v>5179</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3719,21 +3719,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3744,14 +3744,14 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Spångmossen, Spångmossen, Vg</t>
+          <t>Boramossen, Boramossen, Vg</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>470911</v>
+        <v>470799</v>
       </c>
       <c r="R28" t="n">
-        <v>6538981</v>
+        <v>6539107</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3783,7 +3783,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Äldre gnag och kläckhål</t>
+          <t>Äldre gnag och kläckhål.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3825,10 +3825,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130322265</v>
+        <v>130322807</v>
       </c>
       <c r="B29" t="n">
-        <v>5199</v>
+        <v>5179</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3836,21 +3836,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3865,10 +3865,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>470922</v>
+        <v>471012</v>
       </c>
       <c r="R29" t="n">
-        <v>6538911</v>
+        <v>6538879</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -3942,10 +3942,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130322423</v>
+        <v>130323210</v>
       </c>
       <c r="B30" t="n">
-        <v>5199</v>
+        <v>5179</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3953,21 +3953,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3978,14 +3978,14 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Spångmossen, Spångmossen, Vg</t>
+          <t>Boramossen, Boramossen, Vg</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>470869</v>
+        <v>471119</v>
       </c>
       <c r="R30" t="n">
-        <v>6538828</v>
+        <v>6538921</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -4017,7 +4017,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4059,7 +4059,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130322826</v>
+        <v>130321924</v>
       </c>
       <c r="B31" t="n">
         <v>5199</v>
@@ -4099,10 +4099,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>470996</v>
+        <v>470911</v>
       </c>
       <c r="R31" t="n">
-        <v>6538865</v>
+        <v>6538981</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4176,10 +4176,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130111287</v>
+        <v>130322265</v>
       </c>
       <c r="B32" t="n">
-        <v>97986</v>
+        <v>5199</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4187,34 +4187,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221946</v>
+        <v>105930</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>470734</v>
+        <v>470922</v>
       </c>
       <c r="R32" t="n">
-        <v>6539068</v>
+        <v>6538911</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -4241,22 +4246,27 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Äldre gnag och kläckhål</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4283,10 +4293,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130111395</v>
+        <v>130322423</v>
       </c>
       <c r="B33" t="n">
-        <v>97986</v>
+        <v>5199</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4294,34 +4304,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221946</v>
+        <v>105930</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>470886</v>
+        <v>470869</v>
       </c>
       <c r="R33" t="n">
-        <v>6539090</v>
+        <v>6538828</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4348,22 +4363,27 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre gnag och kläckhål</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4387,6 +4407,337 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>130322826</v>
+      </c>
+      <c r="B34" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Spångmossen, Spångmossen, Vg</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>470996</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6538865</v>
+      </c>
+      <c r="S34" t="n">
+        <v>20</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre gnag och kläckhål</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>130111287</v>
+      </c>
+      <c r="B35" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Spångmossen, Spångmossen, Vg</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>470734</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6539068</v>
+      </c>
+      <c r="S35" t="n">
+        <v>20</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>130111395</v>
+      </c>
+      <c r="B36" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Spångmossen, Spångmossen, Vg</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>470886</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6539090</v>
+      </c>
+      <c r="S36" t="n">
+        <v>20</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60589-2025 artfynd.xlsx
+++ b/artfynd/A 60589-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AZ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130324988</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -905,6 +915,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130005289</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1022,6 +1037,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130006694</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1139,6 +1159,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130008089</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1256,6 +1281,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130111482</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1373,6 +1403,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130111555</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1490,6 +1525,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130321743</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1607,6 +1647,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130322056</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1724,6 +1769,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130324876</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1836,6 +1886,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130111747</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1956,6 +2011,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130322176</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2073,6 +2133,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130005860</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2190,6 +2255,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130006116</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2307,6 +2377,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130111348</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2424,6 +2499,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130111912</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2536,6 +2616,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130321685</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2648,6 +2733,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130321917</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2760,6 +2850,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130321939</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2872,6 +2967,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130324271</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3003,6 +3103,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130324653</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3120,6 +3225,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130324834</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3237,6 +3347,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130321613</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3354,6 +3469,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130322032</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3471,6 +3591,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130323305</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3588,6 +3713,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130323532</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3705,6 +3835,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130324686</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3822,6 +3957,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130321696</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3939,6 +4079,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130322807</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4056,6 +4201,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130323210</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4173,6 +4323,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130321924</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4290,6 +4445,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130322265</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4407,6 +4567,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130322423</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4524,6 +4689,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130322826</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4631,6 +4801,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130111287</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4738,8 +4913,50 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130111395</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>